--- a/RAE05X.xlsx
+++ b/RAE05X.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="57">
   <si>
     <t/>
   </si>
   <si>
-    <t>20070537</t>
-  </si>
-  <si>
-    <t>AICE ICE SWT CORN 52</t>
+    <t>20081739</t>
+  </si>
+  <si>
+    <t>AICE ICE MOCHI VAN30</t>
   </si>
   <si>
     <t>RAE05X</t>
@@ -31,12 +31,6 @@
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20081739</t>
-  </si>
-  <si>
-    <t>AICE ICE MOCHI VAN30</t>
-  </si>
-  <si>
     <t>20092473</t>
   </si>
   <si>
@@ -172,25 +166,22 @@
     <t>AICE CHOCO ALMOND110</t>
   </si>
   <si>
+    <t>20138342</t>
+  </si>
+  <si>
+    <t>KALULI CHO MASTER 60</t>
+  </si>
+  <si>
     <t>7</t>
   </si>
   <si>
-    <t>20138342</t>
-  </si>
-  <si>
-    <t>KALULI CHO MASTER 60</t>
+    <t>20141865</t>
+  </si>
+  <si>
+    <t>AICE CHOCO BITES 90</t>
   </si>
   <si>
     <t>8</t>
-  </si>
-  <si>
-    <t>20141865</t>
-  </si>
-  <si>
-    <t>AICE CHOCO BITES 90</t>
-  </si>
-  <si>
-    <t>9</t>
   </si>
 </sst>
 </file>
@@ -583,7 +574,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -667,18 +658,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -687,18 +678,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -707,30 +698,30 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="F7" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -744,10 +735,10 @@
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>5</v>
@@ -764,13 +755,13 @@
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -784,13 +775,13 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -804,53 +795,53 @@
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -864,10 +855,10 @@
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>5</v>
@@ -884,13 +875,13 @@
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -904,13 +895,13 @@
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -924,10 +915,10 @@
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>5</v>
@@ -944,33 +935,33 @@
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -984,13 +975,13 @@
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1004,13 +995,13 @@
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1024,13 +1015,13 @@
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1044,33 +1035,13 @@
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>56</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/RAE05X.xlsx
+++ b/RAE05X.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="44">
   <si>
     <t/>
   </si>
@@ -49,72 +49,60 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20134323</t>
-  </si>
-  <si>
-    <t>AICE MOCHI BANANA45</t>
+    <t>20138344</t>
+  </si>
+  <si>
+    <t>KALULI CHEERS CHEESE</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20138341</t>
+  </si>
+  <si>
+    <t>KALULI YOGHURT 130ML</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20070539</t>
+  </si>
+  <si>
+    <t>AICE CHOCO CRPSY 60G</t>
+  </si>
+  <si>
+    <t>20116496</t>
+  </si>
+  <si>
+    <t>AICE STRAW CRISPY 90</t>
+  </si>
+  <si>
+    <t>20135228</t>
+  </si>
+  <si>
+    <t>AICE CRISPY BALLS 65</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20139397</t>
+  </si>
+  <si>
+    <t>AICE CRS BALL CNC 65</t>
+  </si>
+  <si>
+    <t>20113120</t>
+  </si>
+  <si>
+    <t>AICE CHOCO ALMOND 90</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20134422</t>
-  </si>
-  <si>
-    <t>AICE MOCHI PEACH 45</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20070539</t>
-  </si>
-  <si>
-    <t>AICE CHOCO CRPSY 60G</t>
-  </si>
-  <si>
-    <t>20116496</t>
-  </si>
-  <si>
-    <t>AICE STRAW CRISPY 90</t>
-  </si>
-  <si>
-    <t>20133711</t>
-  </si>
-  <si>
-    <t>AICE BNANA CRISPY 65</t>
-  </si>
-  <si>
-    <t>20135228</t>
-  </si>
-  <si>
-    <t>AICE CRISPY BALLS 65</t>
-  </si>
-  <si>
-    <t>20137858</t>
-  </si>
-  <si>
-    <t>AICE MOCHI MANGO 45</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20139397</t>
-  </si>
-  <si>
-    <t>AICE CRS BALL CNC 65</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20113120</t>
-  </si>
-  <si>
-    <t>AICE CHOCO ALMOND 90</t>
-  </si>
-  <si>
     <t>20126683</t>
   </si>
   <si>
@@ -127,37 +115,10 @@
     <t>AICE HSTRIA MTCHA 70</t>
   </si>
   <si>
-    <t>20103752</t>
-  </si>
-  <si>
-    <t>AICE ICE 3IN1 CLR160</t>
-  </si>
-  <si>
-    <t>20126200</t>
-  </si>
-  <si>
-    <t>AICE CHOCO STRIKE140</t>
-  </si>
-  <si>
-    <t>20106658</t>
-  </si>
-  <si>
-    <t>AICE ICE COOKIES 85G</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
     <t>20134511</t>
   </si>
   <si>
     <t>AICE CLSC CHO ALMD90</t>
-  </si>
-  <si>
-    <t>20136303</t>
-  </si>
-  <si>
-    <t>AICE RIA2 KCG HJU 35</t>
   </si>
   <si>
     <t>20138331</t>
@@ -574,7 +535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -758,7 +719,7 @@
         <v>10</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>11</v>
@@ -766,10 +727,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -786,42 +747,42 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="E12" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -835,13 +796,13 @@
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -855,13 +816,13 @@
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -875,10 +836,10 @@
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>11</v>
@@ -895,152 +856,32 @@
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F23" s="1" t="s">
         <v>11</v>
       </c>
     </row>

--- a/RAE05X.xlsx
+++ b/RAE05X.xlsx
@@ -11,30 +11,36 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="46">
   <si>
     <t/>
   </si>
   <si>
+    <t>20070537</t>
+  </si>
+  <si>
+    <t>AICE ICE SWT CORN 52</t>
+  </si>
+  <si>
+    <t>RAE05X</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
     <t>20081739</t>
   </si>
   <si>
     <t>AICE ICE MOCHI VAN30</t>
   </si>
   <si>
-    <t>RAE05X</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20092473</t>
-  </si>
-  <si>
-    <t>AICE ICE MOCHI CHO45</t>
+    <t>3</t>
   </si>
   <si>
     <t>20132330</t>
@@ -43,7 +49,7 @@
     <t>AICE HSTERIA PEACH70</t>
   </si>
   <si>
-    <t>2</t>
+    <t>4</t>
   </si>
   <si>
     <t>RT,(E-1B)</t>
@@ -55,7 +61,7 @@
     <t>KALULI CHEERS CHEESE</t>
   </si>
   <si>
-    <t>5</t>
+    <t>7</t>
   </si>
   <si>
     <t>20138341</t>
@@ -64,7 +70,7 @@
     <t>KALULI YOGHURT 130ML</t>
   </si>
   <si>
-    <t>6</t>
+    <t>8</t>
   </si>
   <si>
     <t>20070539</t>
@@ -73,19 +79,25 @@
     <t>AICE CHOCO CRPSY 60G</t>
   </si>
   <si>
+    <t>9</t>
+  </si>
+  <si>
     <t>20116496</t>
   </si>
   <si>
     <t>AICE STRAW CRISPY 90</t>
   </si>
   <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>20135228</t>
   </si>
   <si>
     <t>AICE CRISPY BALLS 65</t>
   </si>
   <si>
-    <t>4</t>
+    <t>12</t>
   </si>
   <si>
     <t>20139397</t>
@@ -100,9 +112,6 @@
     <t>AICE CHOCO ALMOND 90</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>20126683</t>
   </si>
   <si>
@@ -133,16 +142,13 @@
     <t>KALULI CHO MASTER 60</t>
   </si>
   <si>
-    <t>7</t>
+    <t>11</t>
   </si>
   <si>
     <t>20141865</t>
   </si>
   <si>
     <t>AICE CHOCO BITES 90</t>
-  </si>
-  <si>
-    <t>8</t>
   </si>
 </sst>
 </file>
@@ -541,7 +547,8 @@
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="5" width="3" customWidth="1"/>
+    <col min="4" max="4" width="3" customWidth="1"/>
+    <col min="5" max="5" width="4" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
@@ -579,18 +586,18 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
@@ -599,18 +606,18 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -619,18 +626,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -639,18 +646,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -659,230 +666,230 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/RAE05X.xlsx
+++ b/RAE05X.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="49">
   <si>
     <t/>
   </si>
@@ -149,6 +149,15 @@
   </si>
   <si>
     <t>AICE CHOCO BITES 90</t>
+  </si>
+  <si>
+    <t>20142571</t>
+  </si>
+  <si>
+    <t>AICE VANCOKIES CUP90</t>
+  </si>
+  <si>
+    <t>13</t>
   </si>
 </sst>
 </file>
@@ -541,7 +550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -892,6 +901,26 @@
         <v>13</v>
       </c>
     </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/RAE05X.xlsx
+++ b/RAE05X.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="52">
   <si>
     <t/>
   </si>
@@ -98,6 +98,15 @@
   </si>
   <si>
     <t>12</t>
+  </si>
+  <si>
+    <t>20142998</t>
+  </si>
+  <si>
+    <t>AICE CRS BALL MSCT65</t>
+  </si>
+  <si>
+    <t>14</t>
   </si>
   <si>
     <t>20139397</t>
@@ -550,7 +559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -752,10 +761,10 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>13</v>
@@ -763,10 +772,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -775,18 +784,18 @@
         <v>5</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -795,7 +804,7 @@
         <v>5</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>6</v>
@@ -803,10 +812,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -815,18 +824,18 @@
         <v>5</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -835,7 +844,7 @@
         <v>5</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>13</v>
@@ -843,10 +852,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -855,7 +864,7 @@
         <v>5</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>13</v>
@@ -863,10 +872,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -875,7 +884,7 @@
         <v>5</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>13</v>
@@ -895,7 +904,7 @@
         <v>5</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>13</v>
@@ -903,10 +912,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -915,9 +924,29 @@
         <v>5</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F18" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>13</v>
       </c>
     </row>

--- a/RAE05X.xlsx
+++ b/RAE05X.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="60">
   <si>
     <t/>
   </si>
@@ -167,6 +167,30 @@
   </si>
   <si>
     <t>13</t>
+  </si>
+  <si>
+    <t>20138920</t>
+  </si>
+  <si>
+    <t>AICE CLSC CHOCO350</t>
+  </si>
+  <si>
+    <t>20141096</t>
+  </si>
+  <si>
+    <t>AICE CHOCO MALLOW350</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>20141097</t>
+  </si>
+  <si>
+    <t>AICE COOKS.CHUNKY350</t>
+  </si>
+  <si>
+    <t>16</t>
   </si>
 </sst>
 </file>
@@ -559,7 +583,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -950,6 +974,66 @@
         <v>13</v>
       </c>
     </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
